--- a/tools/catalog/game_catalog.xlsx
+++ b/tools/catalog/game_catalog.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameMemoirStore\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameMemoirStore\tools\catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A91E44-D412-4E30-8582-19B96613C8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE8F388-4609-4E58-81AB-7E6897EB815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="游戏资料" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>游戏资料</t>
   </si>
@@ -74,151 +61,10 @@
 series_id</t>
   </si>
   <si>
-    <t>distant_signal</t>
-  </si>
-  <si>
-    <t>远星来信</t>
-  </si>
-  <si>
-    <t>微光工作室</t>
-  </si>
-  <si>
     <t>探索冒险</t>
   </si>
   <si>
     <t>在失去联系的边境星球，寻找一封迟到的信。穿过静默的观测站与漫长的星夜，重新连接那些散落在宇宙里的故事。</t>
-  </si>
-  <si>
-    <t>res://assets/art/stars.png</t>
-  </si>
-  <si>
-    <t>iron_frontier</t>
-  </si>
-  <si>
-    <t>钢铁边境</t>
-  </si>
-  <si>
-    <t>北陆互动</t>
-  </si>
-  <si>
-    <t>策略战术</t>
-  </si>
-  <si>
-    <t>在边境建立第一座前哨站。调配有限的补给，规划防线，让每一支小队都能平安归来。</t>
-  </si>
-  <si>
-    <t>res://assets/art/desert.png</t>
-  </si>
-  <si>
-    <t>mist_valley</t>
-  </si>
-  <si>
-    <t>雾谷手记</t>
-  </si>
-  <si>
-    <t>雨后制作组</t>
-  </si>
-  <si>
-    <t>生活模拟</t>
-  </si>
-  <si>
-    <t>修好山谷里的老房子，种下第一批作物。在季节与日常之间，记录属于自己的小小生活。</t>
-  </si>
-  <si>
-    <t>res://assets/art/valley.png</t>
-  </si>
-  <si>
-    <t>last_lighthouse</t>
-  </si>
-  <si>
-    <t>最后一座灯塔</t>
-  </si>
-  <si>
-    <t>潮汐游戏</t>
-  </si>
-  <si>
-    <t>一座灯塔，一片不再平静的海。修复失灵的信号装置，在潮汐退去之前解开岛上的秘密。</t>
-  </si>
-  <si>
-    <t>res://assets/art/ocean.png</t>
-  </si>
-  <si>
-    <t>midnight_castle</t>
-  </si>
-  <si>
-    <t>午夜回廊</t>
-  </si>
-  <si>
-    <t>黑曜石猫制作组</t>
-  </si>
-  <si>
-    <t>角色扮演</t>
-  </si>
-  <si>
-    <t>当钟声响起，古堡的房间会重新排列。带着仅有的地图走进回廊，寻找通往黎明的出口。</t>
-  </si>
-  <si>
-    <t>res://assets/art/castle.png</t>
-  </si>
-  <si>
-    <t>eastbound</t>
-  </si>
-  <si>
-    <t>向东的列车</t>
-  </si>
-  <si>
-    <t>纸飞机工作室</t>
-  </si>
-  <si>
-    <t>登上清晨出发的慢车，在陌生的站台短暂停留。收集沿途的风景，也收集旅人的故事。</t>
-  </si>
-  <si>
-    <t>res://assets/art/train.png</t>
-  </si>
-  <si>
-    <t>forgotten_sands</t>
-  </si>
-  <si>
-    <t>遗忘之沙</t>
-  </si>
-  <si>
-    <t>流沙工作室</t>
-  </si>
-  <si>
-    <t>沿着地图上的最后一条线索，走进一段尚未被记录的旅程。探索未知，做出自己的选择，并将沿途的故事留在游戏回忆录中。</t>
-  </si>
-  <si>
-    <t>forest_path</t>
-  </si>
-  <si>
-    <t>林间小径</t>
-  </si>
-  <si>
-    <t>四季制作组</t>
-  </si>
-  <si>
-    <t>frozen_watch</t>
-  </si>
-  <si>
-    <t>雪境守望</t>
-  </si>
-  <si>
-    <t>blue_hour</t>
-  </si>
-  <si>
-    <t>蓝色时刻</t>
-  </si>
-  <si>
-    <t>orbital_rail</t>
-  </si>
-  <si>
-    <t>轨道旅人</t>
-  </si>
-  <si>
-    <t>ancient_signal</t>
-  </si>
-  <si>
-    <t>古老的信号</t>
   </si>
   <si>
     <r>
@@ -322,12 +168,36 @@
     <t>COREI5-10600K</t>
     <phoneticPr fontId="6"/>
   </si>
+  <si>
+    <t>游戏原型</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>反恐精英</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>反击小队</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>CounterSquad</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>Valse</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>res://assets/art/CounterSquad</t>
+    <phoneticPr fontId="6"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -409,6 +279,21 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -451,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -489,12 +374,37 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <name val="WenQuanYi Micro Hei"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -516,12 +426,6 @@
           <bgColor rgb="FFFDE7E7"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -689,6 +593,12 @@
       </fill>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -703,23 +613,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="GameData" displayName="GameData" ref="A3:N15" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A3:N15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="参与导出_x000a_enabled" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="游戏ID_x000a_game_id" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="游戏名称_x000a_title" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="预告月份_x000a_announce_ym" dataDxfId="14" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="上架月份_x000a_store_release_ym" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="下架月份_x000a_delist_ym" dataDxfId="12" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="首发原价_x000a_base_price" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="开发商_x000a_developer" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="游戏类型_x000a_genres" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{44235653-06E7-41FE-B281-D7263EEFB403}" name="CPU" dataDxfId="8" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{C1380FF9-0AA4-4561-872F-A3F4A77F7584}" name="GPU" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="系列ID_x000a_series_id" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="介绍_x000a_description" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="封面_x000a_capsule" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="GameData" displayName="GameData" ref="A3:O15" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A3:O15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="参与导出_x000a_enabled" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{DE758E1A-A18B-401D-B868-7C97D2E561EB}" name="游戏原型" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="游戏ID_x000a_game_id" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="游戏名称_x000a_title" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="预告月份_x000a_announce_ym" dataDxfId="13" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="上架月份_x000a_store_release_ym" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="下架月份_x000a_delist_ym" dataDxfId="11" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="首发原价_x000a_base_price" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="开发商_x000a_developer" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="游戏类型_x000a_genres" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{44235653-06E7-41FE-B281-D7263EEFB403}" name="CPU" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{C1380FF9-0AA4-4561-872F-A3F4A77F7584}" name="GPU" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="系列ID_x000a_series_id" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="介绍_x000a_description" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="封面_x000a_capsule" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -923,27 +834,27 @@
   <sheetPr>
     <tabColor rgb="FF356784"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:Q23"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="6" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="6" customWidth="1"/>
-    <col min="6" max="6" width="9" style="6"/>
-    <col min="7" max="7" width="16" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="6" customWidth="1"/>
-    <col min="10" max="10" width="15.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="19" style="6" customWidth="1"/>
-    <col min="15" max="15" width="48" style="6" customWidth="1"/>
-    <col min="16" max="16" width="42" style="6" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="6"/>
+    <col min="1" max="2" width="13.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.9375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9" style="6"/>
+    <col min="8" max="8" width="16" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="6" customWidth="1"/>
+    <col min="11" max="11" width="15.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="19" style="6" customWidth="1"/>
+    <col min="16" max="16" width="48" style="6" customWidth="1"/>
+    <col min="17" max="17" width="42" style="6" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -958,12 +869,13 @@
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
-    </row>
-    <row r="2" spans="1:16" ht="20.25">
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" spans="1:17" ht="20.65">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -976,562 +888,294 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:16" ht="33">
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" ht="31.9">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="N3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15">
       <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>200309</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>88</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="K4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
-        <v>200309</v>
-      </c>
-      <c r="F4" s="11">
-        <v>0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>88</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="9">
-        <v>1</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9">
-        <v>200309</v>
-      </c>
-      <c r="F5" s="11">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>72</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="O4" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="9">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>200309</v>
-      </c>
-      <c r="F6" s="11">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>48</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
       <c r="L6" s="12"/>
-      <c r="M6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="9">
-        <v>1</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>200309</v>
-      </c>
-      <c r="F7" s="11">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>60</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="9">
-        <v>1</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
-        <v>200310</v>
-      </c>
-      <c r="F8" s="11">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>96</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="9">
-        <v>1</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
-        <v>200311</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>52</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
       <c r="L9" s="12"/>
-      <c r="M9" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="9">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>200309</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>68</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="9">
-        <v>1</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9">
-        <v>200309</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>42</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="9">
-        <v>1</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
-        <v>200310</v>
-      </c>
-      <c r="F12" s="11">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>92</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
       <c r="L12" s="12"/>
-      <c r="M12" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="9">
-        <v>1</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
-        <v>200310</v>
-      </c>
-      <c r="F13" s="11">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>56</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="9">
-        <v>1</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9">
-        <v>200311</v>
-      </c>
-      <c r="F14" s="11">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>84</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
       <c r="L14" s="12"/>
-      <c r="M14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="9">
-        <v>1</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9">
-        <v>200312</v>
-      </c>
-      <c r="F15" s="11">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>110</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
@@ -1541,14 +1185,15 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
@@ -1558,14 +1203,15 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="F18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
@@ -1575,14 +1221,15 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
@@ -1592,14 +1239,15 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -1609,14 +1257,15 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="F21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -1626,14 +1275,15 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="F22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -1643,14 +1293,15 @@
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="F23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -1660,29 +1311,30 @@
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>
-  <conditionalFormatting sqref="B4:B2003">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(B4&lt;&gt;"",COUNTIFS($B$4:$B$2003,B4)&gt;1)</formula>
+  <conditionalFormatting sqref="C4:C2003">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>AND(C4&lt;&gt;"",COUNTIFS($C$4:$C$2003,C4)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M16:M2003">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(M16&lt;&gt;"",OR(M16&lt;0,M16&gt;100))</formula>
+  <conditionalFormatting sqref="N16:N2003">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND(N16&lt;&gt;"",OR(N16&lt;0,N16&gt;100))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="whole" sqref="A4:A2003" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" sqref="A4:B2003" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="D4:G2003 L16:L2003" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" sqref="E4:H2003 M16:M2003" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="M16:M2003" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="whole" sqref="N16:N2003" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>

--- a/tools/catalog/game_catalog.xlsx
+++ b/tools/catalog/game_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameMemoirStore\tools\catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE8F388-4609-4E58-81AB-7E6897EB815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24572FBD-BD2C-4CDC-A179-EBCF95BCFDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,10 +29,6 @@
 enabled</t>
   </si>
   <si>
-    <t>游戏ID
-game_id</t>
-  </si>
-  <si>
     <t>游戏名称
 title</t>
   </si>
@@ -59,12 +55,6 @@
   <si>
     <t>系列ID
 series_id</t>
-  </si>
-  <si>
-    <t>探索冒险</t>
-  </si>
-  <si>
-    <t>在失去联系的边境星球，寻找一封迟到的信。穿过静默的观测站与漫长的星夜，重新连接那些散落在宇宙里的故事。</t>
   </si>
   <si>
     <r>
@@ -190,6 +180,39 @@
   </si>
   <si>
     <t>res://assets/art/CounterSquad</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>射击/动作/多人</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>二十多年来，在全球数百万玩家的共同铸就下，CounterSquad 提供了精湛绝伦的竞技体验。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ID
+game_id</t>
+    </r>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -336,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -378,6 +401,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -386,25 +412,6 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF245B8C"/>
-        <name val="WenQuanYi Micro Hei"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -585,6 +592,25 @@
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <name val="WenQuanYi Micro Hei"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -617,20 +643,20 @@
   <autoFilter ref="A3:O15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="参与导出_x000a_enabled" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{DE758E1A-A18B-401D-B868-7C97D2E561EB}" name="游戏原型" dataDxfId="0" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="游戏ID_x000a_game_id" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="游戏名称_x000a_title" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="预告月份_x000a_announce_ym" dataDxfId="13" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="上架月份_x000a_store_release_ym" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="下架月份_x000a_delist_ym" dataDxfId="11" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="首发原价_x000a_base_price" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="开发商_x000a_developer" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="游戏类型_x000a_genres" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{44235653-06E7-41FE-B281-D7263EEFB403}" name="CPU" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{C1380FF9-0AA4-4561-872F-A3F4A77F7584}" name="GPU" dataDxfId="6" dataCellStyle="Normal"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="系列ID_x000a_series_id" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="介绍_x000a_description" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="封面_x000a_capsule" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{DE758E1A-A18B-401D-B868-7C97D2E561EB}" name="游戏原型" dataDxfId="15" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="游戏ID_x000a_game_id" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="游戏名称_x000a_title" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="预告月份_x000a_announce_ym" dataDxfId="12" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="上架月份_x000a_store_release_ym" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="下架月份_x000a_delist_ym" dataDxfId="10" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="首发原价_x000a_base_price" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="开发商_x000a_developer" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="游戏类型_x000a_genres" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{44235653-06E7-41FE-B281-D7263EEFB403}" name="CPU" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{C1380FF9-0AA4-4561-872F-A3F4A77F7584}" name="GPU" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="系列ID_x000a_series_id" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="介绍_x000a_description" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="封面_x000a_capsule" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -895,46 +921,46 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="15">
@@ -942,13 +968,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
@@ -960,26 +986,26 @@
         <v>0</v>
       </c>
       <c r="H4" s="9">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="I4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12" t="s">
-        <v>11</v>
-      </c>
       <c r="O4" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1316,12 +1342,12 @@
   </sheetData>
   <phoneticPr fontId="6"/>
   <conditionalFormatting sqref="C4:C2003">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(C4&lt;&gt;"",COUNTIFS($C$4:$C$2003,C4)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:N2003">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(N16&lt;&gt;"",OR(N16&lt;0,N16&gt;100))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tools/catalog/game_catalog.xlsx
+++ b/tools/catalog/game_catalog.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameMemoirStore\tools\catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameMemoirStore\tools\catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24572FBD-BD2C-4CDC-A179-EBCF95BCFDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75686DFE-6372-42FB-B76F-AB645B0FD193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="游戏资料" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>游戏资料</t>
   </si>
@@ -151,14 +164,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>RTX3060</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>COREI5-10600K</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>游戏原型</t>
     <phoneticPr fontId="6"/>
   </si>
@@ -172,10 +177,6 @@
   </si>
   <si>
     <t>CounterSquad</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>Valse</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -212,6 +213,154 @@
       </rPr>
       <t>ID
 game_id</t>
+    </r>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>CTA</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>马克思佩恩2</t>
+  </si>
+  <si>
+    <t>使命召唤</t>
+  </si>
+  <si>
+    <t>极品飞车</t>
+  </si>
+  <si>
+    <t>FuckStar</t>
+  </si>
+  <si>
+    <t>FuckStar</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>Vcompany</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>动作</t>
+  </si>
+  <si>
+    <t>动作</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>魔兽争霸Ⅲ</t>
+  </si>
+  <si>
+    <t>GTA3</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>CTA3</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="BIZ UDGothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>城市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偷车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="WenQuanYi Micro Hei"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>GTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>罪恶都市</t>
+    </r>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <t>CTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>BadCity</t>
+    </r>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>城市偷车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>恶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF245B8C"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>都</t>
     </r>
     <phoneticPr fontId="6"/>
   </si>
@@ -220,7 +369,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -317,6 +466,54 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="BIZ UDGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="WenQuanYi Micro Hei"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="Noto Sans JP"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="Noto Sans JP"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF245B8C"/>
+      <name val="Calibri"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="4">
@@ -359,7 +556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -406,10 +603,28 @@
     <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
     <dxf>
@@ -861,13 +1076,14 @@
     <tabColor rgb="FF356784"/>
   </sheetPr>
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="13.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.9375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
     <col min="7" max="7" width="9" style="6"/>
     <col min="8" max="8" width="16" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.125" style="6" bestFit="1" customWidth="1"/>
@@ -897,7 +1113,7 @@
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:17" ht="20.65">
+    <row r="2" spans="1:17" ht="20.25">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -916,15 +1132,15 @@
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
     </row>
-    <row r="3" spans="1:17" ht="31.9">
+    <row r="3" spans="1:17" ht="45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -963,18 +1179,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15">
+    <row r="4" spans="1:17" ht="16.5">
       <c r="A4" s="9">
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>19</v>
-      </c>
       <c r="D4" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
@@ -989,62 +1205,94 @@
         <v>105</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="18">
       <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="B5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>200309</v>
+      </c>
       <c r="G5" s="11"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="12"/>
+      <c r="H5" s="9">
+        <v>350</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>30</v>
+      </c>
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="M5" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" ht="18">
       <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="B6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>200309</v>
+      </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="12"/>
+      <c r="H6" s="9">
+        <v>350</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="K6" s="12"/>
       <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="M6" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" ht="18">
       <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1059,9 +1307,11 @@
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" ht="18">
       <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
+      <c r="B8" s="19" t="s">
+        <v>31</v>
+      </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
@@ -1076,9 +1326,11 @@
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" ht="18">
       <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="19" t="s">
+        <v>23</v>
+      </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="9"/>
@@ -1095,7 +1347,9 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
@@ -1112,7 +1366,9 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="B11" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="9"/>
@@ -1341,7 +1597,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>
-  <conditionalFormatting sqref="C4:C2003">
+  <conditionalFormatting sqref="C4:C5 C7:C2003">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(C4&lt;&gt;"",COUNTIFS($C$4:$C$2003,C4)&gt;1)</formula>
     </cfRule>
@@ -1352,11 +1608,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="whole" sqref="A4:B2003" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" sqref="A4:B2003 C6" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="E4:H2003 M16:M2003" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" sqref="M16:M2003 E4:H2003" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>

--- a/tools/catalog/game_catalog.xlsx
+++ b/tools/catalog/game_catalog.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameMemoirStore\tools\catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameMemoirStore\tools\catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52532340-9DF9-4FA1-AB36-51FCFD1CC132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEA1FD1-A242-4038-BB31-A17850F67DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3645" yWindow="3645" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="游戏资料" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -267,7 +267,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -296,7 +296,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -325,7 +325,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -354,7 +354,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -383,7 +383,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -412,7 +412,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -441,7 +441,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -473,7 +473,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -502,7 +502,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -531,7 +531,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -651,14 +651,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -669,7 +669,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -747,7 +747,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{64843DEA-5192-490E-B98B-75B046B68538}"/>
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1026,25 +1026,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="14.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.73046875" style="4" customWidth="1"/>
     <col min="6" max="6" width="19" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.86328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.86328125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.46484375" style="4" customWidth="1"/>
     <col min="10" max="10" width="15" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="4"/>
-    <col min="13" max="13" width="10.25" style="4" customWidth="1"/>
-    <col min="14" max="14" width="12.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="10.265625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="12.73046875" style="4" customWidth="1"/>
     <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="54">
+    <row r="1" spans="1:14" ht="36">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1156,9 +1156,6 @@
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
@@ -1191,9 +1188,6 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
@@ -1226,9 +1220,6 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
       <c r="B6" s="4" t="s">
         <v>33</v>
       </c>
@@ -1261,9 +1252,6 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="4">
-        <v>1</v>
-      </c>
       <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
@@ -1296,9 +1284,6 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="4">
-        <v>1</v>
-      </c>
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
@@ -1328,9 +1313,6 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="4">
-        <v>1</v>
-      </c>
       <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1360,9 +1342,6 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="4">
-        <v>1</v>
-      </c>
       <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1392,9 +1371,6 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="4">
-        <v>1</v>
-      </c>
       <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
@@ -1427,9 +1403,6 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="4">
-        <v>1</v>
-      </c>
       <c r="B12" s="4" t="s">
         <v>54</v>
       </c>
@@ -1462,9 +1435,6 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="4">
-        <v>1</v>
-      </c>
       <c r="B13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1496,10 +1466,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="18.75">
-      <c r="A14" s="4">
-        <v>1</v>
-      </c>
+    <row r="14" spans="1:14">
       <c r="B14" s="4" t="s">
         <v>56</v>
       </c>
@@ -1532,9 +1499,6 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="4">
-        <v>1</v>
-      </c>
       <c r="B15" s="4" t="s">
         <v>57</v>
       </c>
@@ -1566,10 +1530,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="18.75">
-      <c r="A16" s="4">
-        <v>1</v>
-      </c>
+    <row r="16" spans="1:14">
       <c r="B16" s="4" t="s">
         <v>58</v>
       </c>
@@ -1601,10 +1562,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="4">
-        <v>1</v>
-      </c>
+    <row r="17" spans="2:13">
       <c r="B17" s="4" t="s">
         <v>59</v>
       </c>
@@ -1636,10 +1594,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18.75">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
+    <row r="18" spans="2:13">
       <c r="B18" s="4" t="s">
         <v>60</v>
       </c>
@@ -1671,10 +1626,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="4">
-        <v>1</v>
-      </c>
+    <row r="19" spans="2:13">
       <c r="B19" s="4" t="s">
         <v>61</v>
       </c>
@@ -1706,10 +1658,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18.75">
-      <c r="A20" s="4">
-        <v>1</v>
-      </c>
+    <row r="20" spans="2:13">
       <c r="B20" s="4" t="s">
         <v>62</v>
       </c>
@@ -1741,10 +1690,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="4">
-        <v>1</v>
-      </c>
+    <row r="21" spans="2:13">
       <c r="B21" s="4" t="s">
         <v>63</v>
       </c>
@@ -1776,10 +1722,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.75">
-      <c r="A22" s="4">
-        <v>1</v>
-      </c>
+    <row r="22" spans="2:13">
       <c r="B22" s="4" t="s">
         <v>64</v>
       </c>
@@ -1811,10 +1754,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="4">
-        <v>1</v>
-      </c>
+    <row r="23" spans="2:13">
       <c r="B23" s="4" t="s">
         <v>65</v>
       </c>
@@ -1846,10 +1786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="18.75">
-      <c r="A24" s="4">
-        <v>1</v>
-      </c>
+    <row r="24" spans="2:13">
       <c r="B24" s="4" t="s">
         <v>66</v>
       </c>
@@ -1881,10 +1818,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="4">
-        <v>1</v>
-      </c>
+    <row r="25" spans="2:13">
       <c r="B25" s="4" t="s">
         <v>67</v>
       </c>
@@ -1916,10 +1850,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75">
-      <c r="A26" s="4">
-        <v>1</v>
-      </c>
+    <row r="26" spans="2:13">
       <c r="B26" s="4" t="s">
         <v>68</v>
       </c>
@@ -1951,10 +1882,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="4">
-        <v>1</v>
-      </c>
+    <row r="27" spans="2:13">
       <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
@@ -1986,10 +1914,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="4">
-        <v>1</v>
-      </c>
+    <row r="28" spans="2:13">
       <c r="B28" s="4" t="s">
         <v>70</v>
       </c>
@@ -2021,10 +1946,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="18.75">
-      <c r="A29" s="4">
-        <v>1</v>
-      </c>
+    <row r="29" spans="2:13">
       <c r="B29" s="4" t="s">
         <v>71</v>
       </c>
@@ -2056,10 +1978,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="4">
-        <v>1</v>
-      </c>
+    <row r="30" spans="2:13">
       <c r="B30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2091,10 +2010,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="18.75">
-      <c r="A31" s="4">
-        <v>1</v>
-      </c>
+    <row r="31" spans="2:13">
       <c r="B31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2126,10 +2042,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="4">
-        <v>1</v>
-      </c>
+    <row r="32" spans="2:13">
       <c r="B32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2161,10 +2074,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="18.75">
-      <c r="A33" s="4">
-        <v>1</v>
-      </c>
+    <row r="33" spans="2:13">
       <c r="B33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2196,7 +2106,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="2:13">
       <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
@@ -2210,9 +2120,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21089BE2-1E35-470B-A5C8-156020EEAD12}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -2231,7 +2141,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
@@ -2250,7 +2160,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="18">
       <c r="A3" s="2" t="s">
         <v>100</v>
       </c>
@@ -2271,7 +2181,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="18">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -2290,7 +2200,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" ht="18">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2305,7 +2215,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" ht="18">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2320,7 +2230,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" ht="18">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2335,7 +2245,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" ht="18">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2350,7 +2260,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="18">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
@@ -2365,7 +2275,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" ht="18">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
